--- a/artfynd/A 3567-2024 artfynd.xlsx
+++ b/artfynd/A 3567-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3567-2024 artfynd.xlsx
+++ b/artfynd/A 3567-2024 artfynd.xlsx
@@ -675,54 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114567364</v>
+        <v>114570621</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2779</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Munga-Horndal, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582966</v>
+        <v>582956</v>
       </c>
       <c r="R2" t="n">
-        <v>6650775</v>
+        <v>6650779</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,6 +758,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -774,61 +770,56 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mårten Nilsson, Louise Almén</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114567365</v>
+        <v>114570622</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2779</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Munga-Horndal, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582944</v>
+        <v>582962</v>
       </c>
       <c r="R3" t="n">
-        <v>6650780</v>
+        <v>6650895</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,6 +860,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -880,22 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mårten Nilsson, Louise Almén</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114570621</v>
+        <v>114571556</v>
       </c>
       <c r="B4" t="n">
-        <v>93952</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,38 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2779</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Munga-Horndal, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582956</v>
+        <v>582928</v>
       </c>
       <c r="R4" t="n">
-        <v>6650779</v>
+        <v>6650855</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,7 +958,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -994,54 +976,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114570622</v>
+        <v>114567364</v>
       </c>
       <c r="B5" t="n">
-        <v>93952</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2779</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Munga-Horndal, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582962</v>
+        <v>582966</v>
       </c>
       <c r="R5" t="n">
-        <v>6650895</v>
+        <v>6650775</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1059,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1094,57 +1070,56 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Louise Almén</t>
+          <t>Mårten Nilsson, Louise Almén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114571556</v>
+        <v>114567365</v>
       </c>
       <c r="B6" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Munga-Horndal, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582928</v>
+        <v>582944</v>
       </c>
       <c r="R6" t="n">
-        <v>6650855</v>
+        <v>6650780</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,7 +1171,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Louise Almén</t>
+          <t>Mårten Nilsson, Louise Almén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 3567-2024 artfynd.xlsx
+++ b/artfynd/A 3567-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114570621</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114570622</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114571556</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567364</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,8 +1200,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567365</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>